--- a/registration_forms/044_youth_sports_registration_form--registration_forms.xlsx
+++ b/registration_forms/044_youth_sports_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,8 +980,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'disability'}</t>
+          <t>disability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'Disability'}</t>
+          <t>Disability</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'injury_history'}</t>
+          <t>injury_history</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'Injury History'}</t>
+          <t>Injury History</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
